--- a/dcf/NSP.xlsx
+++ b/dcf/NSP.xlsx
@@ -1128,184 +1128,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>65.93176085200874</v>
+        <v>67.6886849474871</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>63.50467231078717</v>
+        <v>65.1799758728563</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>61.19326627137199</v>
+        <v>62.79110093033751</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>58.99137642780026</v>
+        <v>60.51566450766479</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>56.89319563653084</v>
+        <v>58.34764381258894</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>54.89325333226547</v>
+        <v>56.28136541668111</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>52.98639446469906</v>
+        <v>54.31148337944789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>70.32407109070469</v>
+        <v>72.08099518618306</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>67.69293121596003</v>
+        <v>69.36823477802918</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>65.18785291878577</v>
+        <v>66.78568757775129</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>62.80209662746157</v>
+        <v>64.3263847073261</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>60.52931607667609</v>
+        <v>61.98376425273419</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>58.36353354330459</v>
+        <v>59.75164562772023</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>56.29911675157114</v>
+        <v>57.62420566631997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.71638132940065</v>
+        <v>76.47330542487902</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>71.88119012113287</v>
+        <v>73.55649368320202</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>69.18243956619955</v>
+        <v>70.78027422516507</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>66.61281682712287</v>
+        <v>68.1371049069874</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>64.16543651682133</v>
+        <v>65.61988469287944</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>61.83381375434371</v>
+        <v>63.22192583875935</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>59.61183903844324</v>
+        <v>60.93692795319207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>79.10869156809657</v>
+        <v>80.86561566357497</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>76.06944902630573</v>
+        <v>77.74475258837489</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>73.17702621361333</v>
+        <v>74.77486087257884</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>70.42353702678419</v>
+        <v>71.94782510664871</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>67.80155695696658</v>
+        <v>69.25600513302469</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>65.30409396538282</v>
+        <v>66.69220604979847</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>62.92456132531532</v>
+        <v>64.24965024006414</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>83.50100180679253</v>
+        <v>85.25792590227093</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>80.25770793147859</v>
+        <v>81.93301149354774</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>77.1716128610271</v>
+        <v>78.76944751999262</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>74.23425722644549</v>
+        <v>75.75854530631001</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>71.43767739711183</v>
+        <v>72.89212557316993</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>68.77437417642193</v>
+        <v>70.16248626083758</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>66.2372836121874</v>
+        <v>67.56237252693624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>87.89331204548849</v>
+        <v>89.65023614096688</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>84.44596683665145</v>
+        <v>86.1212703987206</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>81.16619950844088</v>
+        <v>82.76403416740641</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>78.0449774261068</v>
+        <v>79.56926550597132</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>75.07379783725706</v>
+        <v>76.52824601331518</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>72.24465438746105</v>
+        <v>73.63276647187671</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>69.55000589905949</v>
+        <v>70.87509481380832</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>92.28562228418444</v>
+        <v>94.04254637966284</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>88.6342257418243</v>
+        <v>90.30952930389344</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>85.16078615585467</v>
+        <v>86.75862081482018</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>81.8556976257681</v>
+        <v>83.37998570563262</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>78.70991827740231</v>
+        <v>80.16436645346042</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>75.71493459850016</v>
+        <v>77.10304668291582</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>72.86272818593157</v>
+        <v>74.18781710068041</v>
       </c>
     </row>
     <row r="13">
@@ -1328,7 +1328,7 @@
         <v>0.06357957884747187</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9236672262253399</v>
+        <v>0.921329947136165</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="46">
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>70.42353702678419</v>
+        <v>71.94782510664871</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>168.4777564027932</v>
+        <v>171.7752957139245</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>9.035987073404039</v>
+        <v>9.300383580688321</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/NSP.xlsx
+++ b/dcf/NSP.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
